--- a/docs/EdVidura_Requirements_CrossCheck_closed.xlsx
+++ b/docs/EdVidura_Requirements_CrossCheck_closed.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>Now (27 Oct 2026)</t>
+          <t>Now (28 Oct 2026)</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
@@ -2496,19 +2496,19 @@
           <t>AI question bank from Technical Orders and uploads (20+ per document)</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>Not implemented</t>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Implemented (code present)</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>No Technical Order ingestion; AI draft from PDF exists but is not a TO bank</t>
+          <t>POST /api/v1/app/cat/bank drafts 20+ items from TO text or PDF/DOCX; SPA Checkpoint CAT generator; review then promote</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Build TO ingestion and bank generation</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2518,10 +2518,14 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>Not started this phase</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr"/>
+          <t>Live 20+ TO question bank on Checkpoint</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>https://edvidura-app-production.up.railway.app/app/#quiz</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2633,19 +2637,19 @@
           <t>AI competency mapper</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>Not implemented</t>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Implemented (code present)</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Competency maps come from a manually maintained skills registry, not AI extraction</t>
+          <t>POST /api/v1/app/cat/map extracts TO/EO/objective lines and matches or proposes skills; Diagnostics CAT mapper + proposal approve</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Build AI extraction from TOs</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2655,10 +2659,14 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>Not started this phase</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr"/>
+          <t>Live AI competency mapper on Diagnostics</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>https://edvidura-app-production.up.railway.app/app/#teacher-diagnostics</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4664,37 +4672,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4842,13 +4852,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -4996,13 +5006,13 @@
         <v>83</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -5120,7 +5130,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>XR store, LTI groups, essay RAG, AR recorder, 100+ test bank, ML PLE</t>
+          <t>XR store, ML PLE, AR recorder, ADA checker, ETIMS, semantic search</t>
         </is>
       </c>
     </row>
